--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$U$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$V$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>退货入库单号</t>
   </si>
@@ -41,6 +41,9 @@
     <t>第三方单据编号</t>
   </si>
   <si>
+    <t>退货物流单号</t>
+  </si>
+  <si>
     <t>单据类型</t>
   </si>
   <si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t>{.thirdCode}</t>
+  </si>
+  <si>
+    <t>{.returnLogisticCode}</t>
   </si>
   <si>
     <t>{.type}</t>
@@ -1129,26 +1135,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="9.75" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="24.625" customWidth="1"/>
-    <col min="7" max="7" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="8.25" customWidth="1"/>
-    <col min="10" max="10" width="24.625" customWidth="1"/>
-    <col min="11" max="12" width="13.125" customWidth="1"/>
-    <col min="13" max="14" width="12.75" customWidth="1"/>
-    <col min="15" max="16" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="1" max="4" width="14.25" customWidth="1"/>
+    <col min="5" max="5" width="9.75" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="7" max="7" width="24.625" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="8.25" customWidth="1"/>
+    <col min="11" max="11" width="24.625" customWidth="1"/>
+    <col min="12" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="15" width="12.75" customWidth="1"/>
+    <col min="16" max="17" width="11.875" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:21">
+    <row r="1" customFormat="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,70 +1218,76 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="O2" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="P2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="Q2" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="R2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -10,7 +10,7 @@
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$W$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>退货入库单号</t>
   </si>
@@ -59,6 +59,9 @@
     <t>作废状态</t>
   </si>
   <si>
+    <t>仓库</t>
+  </si>
+  <si>
     <t>sku</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1135,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="4" width="14.25" customWidth="1"/>
@@ -1143,18 +1149,19 @@
     <col min="6" max="6" width="20.125" customWidth="1"/>
     <col min="7" max="7" width="24.625" customWidth="1"/>
     <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="24.625" customWidth="1"/>
-    <col min="12" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="17" width="11.875" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="24.625" customWidth="1"/>
+    <col min="13" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="16" width="12.75" customWidth="1"/>
+    <col min="17" max="18" width="11.875" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="9.625" customWidth="1"/>
+    <col min="22" max="22" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:22">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1221,73 +1228,79 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="Q2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="R2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="S2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -10,7 +10,7 @@
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$AC$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>退货入库单号</t>
   </si>
@@ -86,6 +86,24 @@
     <t>实退数量</t>
   </si>
   <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t>汇率</t>
+  </si>
+  <si>
+    <t>退货金额</t>
+  </si>
+  <si>
+    <t>含税退货金额</t>
+  </si>
+  <si>
+    <t>退货金额（本位币）</t>
+  </si>
+  <si>
+    <t>含税退货金额（本位币）</t>
+  </si>
+  <si>
     <t>销售员</t>
   </si>
   <si>
@@ -153,6 +171,24 @@
   </si>
   <si>
     <t>{.realQty}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.exchangeRate}</t>
+  </si>
+  <si>
+    <t>{.returnAmount}</t>
+  </si>
+  <si>
+    <t>{.taxReturnAmount}</t>
+  </si>
+  <si>
+    <t>{.returnAmountLocalCurrency}</t>
+  </si>
+  <si>
+    <t>{.taxReturnAmountLocalCurrency}</t>
   </si>
   <si>
     <t>{.sellerName}</t>
@@ -812,11 +848,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1141,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="4" width="14.25" customWidth="1"/>
@@ -1155,13 +1194,13 @@
     <col min="13" max="14" width="13.125" customWidth="1"/>
     <col min="15" max="16" width="12.75" customWidth="1"/>
     <col min="17" max="18" width="11.875" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="9.625" customWidth="1"/>
-    <col min="22" max="22" width="9.375" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="26" max="26" width="13" customWidth="1"/>
+    <col min="27" max="27" width="9.625" customWidth="1"/>
+    <col min="28" max="28" width="9.375" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:23">
+    <row r="1" customFormat="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1216,91 +1255,127 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$AC$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$AD$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>退货入库单号</t>
   </si>
@@ -41,6 +41,9 @@
     <t>第三方单据编号</t>
   </si>
   <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
     <t>退货物流单号</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>{.thirdCode}</t>
+  </si>
+  <si>
+    <t>{.platformOrderCode}</t>
   </si>
   <si>
     <t>{.returnLogisticCode}</t>
@@ -1180,27 +1186,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="9.75" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="7" width="24.625" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="24.625" customWidth="1"/>
-    <col min="13" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="18" width="11.875" customWidth="1"/>
-    <col min="26" max="26" width="13" customWidth="1"/>
-    <col min="27" max="27" width="9.625" customWidth="1"/>
-    <col min="28" max="28" width="9.375" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="1" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="13" max="13" width="24.625" customWidth="1"/>
+    <col min="14" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="17" width="12.75" customWidth="1"/>
+    <col min="18" max="19" width="11.875" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="9.625" customWidth="1"/>
+    <col min="29" max="29" width="9.375" customWidth="1"/>
+    <col min="30" max="30" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:29">
+    <row r="1" customFormat="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1261,7 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -1273,7 +1279,7 @@
       <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
@@ -1288,94 +1294,100 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="Q2" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="R2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="S2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="T2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -35,7 +35,7 @@
     <t>退货入库单号</t>
   </si>
   <si>
-    <t>退货单号</t>
+    <t>来源订单号</t>
   </si>
   <si>
     <t>第三方单据编号</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soReturnInstock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$AC$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$1:$AD$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,17 +30,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>退货入库单号</t>
   </si>
   <si>
-    <t>退货单号</t>
+    <t>来源订单号</t>
   </si>
   <si>
     <t>第三方单据编号</t>
   </si>
   <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
     <t>退货物流单号</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
   </si>
   <si>
     <t>{.thirdCode}</t>
+  </si>
+  <si>
+    <t>{.platformOrderCode}</t>
   </si>
   <si>
     <t>{.returnLogisticCode}</t>
@@ -1180,27 +1186,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="9.75" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="7" width="24.625" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="24.625" customWidth="1"/>
-    <col min="13" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="18" width="11.875" customWidth="1"/>
-    <col min="26" max="26" width="13" customWidth="1"/>
-    <col min="27" max="27" width="9.625" customWidth="1"/>
-    <col min="28" max="28" width="9.375" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="1" max="5" width="14.25" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="13" max="13" width="24.625" customWidth="1"/>
+    <col min="14" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="17" width="12.75" customWidth="1"/>
+    <col min="18" max="19" width="11.875" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="9.625" customWidth="1"/>
+    <col min="29" max="29" width="9.375" customWidth="1"/>
+    <col min="30" max="30" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:29">
+    <row r="1" customFormat="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1261,7 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -1273,7 +1279,7 @@
       <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
@@ -1288,94 +1294,100 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="Q2" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="R2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="S2" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="T2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
